--- a/jpcore-r4/copilot/high-priority-translation-issues/StructureDefinition-jp-medicationrequest.xlsx
+++ b/jpcore-r4/copilot/high-priority-translation-issues/StructureDefinition-jp-medicationrequest.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4148" uniqueCount="670">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4147" uniqueCount="669">
   <si>
     <t>Property</t>
   </si>
@@ -1032,9 +1032,6 @@
   </si>
   <si>
     <t>このMedicationRequestオーダの優先度。他のオーダと比較して表現される。</t>
-  </si>
-  <si>
-    <t>FHIRでは文字列の大きさが1MBを超えてはならない(SHALL NOT)。</t>
   </si>
   <si>
     <t>リクエストの実行に割り当てられる重要性のレベルを特定します。 / Identifies the level of importance to be assigned to actioning the request.</t>
@@ -8491,9 +8488,7 @@
       <c r="M52" t="s" s="2">
         <v>324</v>
       </c>
-      <c r="N52" t="s" s="2">
-        <v>325</v>
-      </c>
+      <c r="N52" s="2"/>
       <c r="O52" s="2"/>
       <c r="P52" t="s" s="2">
         <v>82</v>
@@ -8521,10 +8516,10 @@
         <v>186</v>
       </c>
       <c r="Y52" t="s" s="2">
+        <v>325</v>
+      </c>
+      <c r="Z52" t="s" s="2">
         <v>326</v>
-      </c>
-      <c r="Z52" t="s" s="2">
-        <v>327</v>
       </c>
       <c r="AA52" t="s" s="2">
         <v>82</v>
@@ -8557,16 +8552,16 @@
         <v>103</v>
       </c>
       <c r="AK52" t="s" s="2">
+        <v>327</v>
+      </c>
+      <c r="AL52" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM52" t="s" s="2">
         <v>328</v>
       </c>
-      <c r="AL52" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AM52" t="s" s="2">
+      <c r="AN52" t="s" s="2">
         <v>329</v>
-      </c>
-      <c r="AN52" t="s" s="2">
-        <v>330</v>
       </c>
       <c r="AO52" t="s" s="2">
         <v>82</v>
@@ -8574,10 +8569,10 @@
     </row>
     <row r="53">
       <c r="A53" t="s" s="2">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="C53" s="2"/>
       <c r="D53" t="s" s="2">
@@ -8600,16 +8595,16 @@
         <v>92</v>
       </c>
       <c r="K53" t="s" s="2">
+        <v>331</v>
+      </c>
+      <c r="L53" t="s" s="2">
         <v>332</v>
       </c>
-      <c r="L53" t="s" s="2">
+      <c r="M53" t="s" s="2">
         <v>333</v>
       </c>
-      <c r="M53" t="s" s="2">
+      <c r="N53" t="s" s="2">
         <v>334</v>
-      </c>
-      <c r="N53" t="s" s="2">
-        <v>335</v>
       </c>
       <c r="O53" s="2"/>
       <c r="P53" t="s" s="2">
@@ -8659,7 +8654,7 @@
         <v>82</v>
       </c>
       <c r="AF53" t="s" s="2">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="AG53" t="s" s="2">
         <v>80</v>
@@ -8680,7 +8675,7 @@
         <v>82</v>
       </c>
       <c r="AM53" t="s" s="2">
-        <v>336</v>
+        <v>335</v>
       </c>
       <c r="AN53" t="s" s="2">
         <v>82</v>
@@ -8691,10 +8686,10 @@
     </row>
     <row r="54">
       <c r="A54" t="s" s="2">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="C54" s="2"/>
       <c r="D54" t="s" s="2">
@@ -8717,13 +8712,13 @@
         <v>92</v>
       </c>
       <c r="K54" t="s" s="2">
+        <v>337</v>
+      </c>
+      <c r="L54" t="s" s="2">
         <v>338</v>
       </c>
-      <c r="L54" t="s" s="2">
+      <c r="M54" t="s" s="2">
         <v>339</v>
-      </c>
-      <c r="M54" t="s" s="2">
-        <v>340</v>
       </c>
       <c r="N54" s="2"/>
       <c r="O54" s="2"/>
@@ -8774,7 +8769,7 @@
         <v>82</v>
       </c>
       <c r="AF54" t="s" s="2">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="AG54" t="s" s="2">
         <v>80</v>
@@ -8795,7 +8790,7 @@
         <v>82</v>
       </c>
       <c r="AM54" t="s" s="2">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="AN54" t="s" s="2">
         <v>82</v>
@@ -8806,10 +8801,10 @@
     </row>
     <row r="55">
       <c r="A55" t="s" s="2">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="C55" s="2"/>
       <c r="D55" t="s" s="2">
@@ -8835,13 +8830,13 @@
         <v>193</v>
       </c>
       <c r="L55" t="s" s="2">
+        <v>342</v>
+      </c>
+      <c r="M55" t="s" s="2">
         <v>343</v>
       </c>
-      <c r="M55" t="s" s="2">
+      <c r="N55" t="s" s="2">
         <v>344</v>
-      </c>
-      <c r="N55" t="s" s="2">
-        <v>345</v>
       </c>
       <c r="O55" s="2"/>
       <c r="P55" t="s" s="2">
@@ -8870,11 +8865,11 @@
         <v>115</v>
       </c>
       <c r="Y55" t="s" s="2">
+        <v>345</v>
+      </c>
+      <c r="Z55" t="s" s="2">
         <v>346</v>
       </c>
-      <c r="Z55" t="s" s="2">
-        <v>347</v>
-      </c>
       <c r="AA55" t="s" s="2">
         <v>82</v>
       </c>
@@ -8891,7 +8886,7 @@
         <v>82</v>
       </c>
       <c r="AF55" t="s" s="2">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="AG55" t="s" s="2">
         <v>91</v>
@@ -8906,27 +8901,27 @@
         <v>103</v>
       </c>
       <c r="AK55" t="s" s="2">
+        <v>347</v>
+      </c>
+      <c r="AL55" t="s" s="2">
         <v>348</v>
       </c>
-      <c r="AL55" t="s" s="2">
+      <c r="AM55" t="s" s="2">
         <v>349</v>
       </c>
-      <c r="AM55" t="s" s="2">
+      <c r="AN55" t="s" s="2">
         <v>350</v>
       </c>
-      <c r="AN55" t="s" s="2">
+      <c r="AO55" t="s" s="2">
         <v>351</v>
-      </c>
-      <c r="AO55" t="s" s="2">
-        <v>352</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="s" s="2">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="C56" s="2"/>
       <c r="D56" t="s" s="2">
@@ -8949,16 +8944,16 @@
         <v>92</v>
       </c>
       <c r="K56" t="s" s="2">
+        <v>353</v>
+      </c>
+      <c r="L56" t="s" s="2">
         <v>354</v>
       </c>
-      <c r="L56" t="s" s="2">
+      <c r="M56" t="s" s="2">
         <v>355</v>
       </c>
-      <c r="M56" t="s" s="2">
+      <c r="N56" t="s" s="2">
         <v>356</v>
-      </c>
-      <c r="N56" t="s" s="2">
-        <v>357</v>
       </c>
       <c r="O56" s="2"/>
       <c r="P56" t="s" s="2">
@@ -9008,7 +9003,7 @@
         <v>82</v>
       </c>
       <c r="AF56" t="s" s="2">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="AG56" t="s" s="2">
         <v>91</v>
@@ -9023,27 +9018,27 @@
         <v>103</v>
       </c>
       <c r="AK56" t="s" s="2">
+        <v>357</v>
+      </c>
+      <c r="AL56" t="s" s="2">
         <v>358</v>
       </c>
-      <c r="AL56" t="s" s="2">
+      <c r="AM56" t="s" s="2">
         <v>359</v>
       </c>
-      <c r="AM56" t="s" s="2">
+      <c r="AN56" t="s" s="2">
         <v>360</v>
       </c>
-      <c r="AN56" t="s" s="2">
+      <c r="AO56" t="s" s="2">
         <v>361</v>
-      </c>
-      <c r="AO56" t="s" s="2">
-        <v>362</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="s" s="2">
-        <v>363</v>
+        <v>362</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>363</v>
+        <v>362</v>
       </c>
       <c r="C57" s="2"/>
       <c r="D57" t="s" s="2">
@@ -9066,16 +9061,16 @@
         <v>82</v>
       </c>
       <c r="K57" t="s" s="2">
+        <v>363</v>
+      </c>
+      <c r="L57" t="s" s="2">
         <v>364</v>
       </c>
-      <c r="L57" t="s" s="2">
+      <c r="M57" t="s" s="2">
         <v>365</v>
       </c>
-      <c r="M57" t="s" s="2">
+      <c r="N57" t="s" s="2">
         <v>366</v>
-      </c>
-      <c r="N57" t="s" s="2">
-        <v>367</v>
       </c>
       <c r="O57" s="2"/>
       <c r="P57" t="s" s="2">
@@ -9125,7 +9120,7 @@
         <v>82</v>
       </c>
       <c r="AF57" t="s" s="2">
-        <v>363</v>
+        <v>362</v>
       </c>
       <c r="AG57" t="s" s="2">
         <v>80</v>
@@ -9140,27 +9135,27 @@
         <v>103</v>
       </c>
       <c r="AK57" t="s" s="2">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="AL57" t="s" s="2">
         <v>295</v>
       </c>
       <c r="AM57" t="s" s="2">
+        <v>368</v>
+      </c>
+      <c r="AN57" t="s" s="2">
         <v>369</v>
       </c>
-      <c r="AN57" t="s" s="2">
+      <c r="AO57" t="s" s="2">
         <v>370</v>
-      </c>
-      <c r="AO57" t="s" s="2">
-        <v>371</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="s" s="2">
-        <v>372</v>
+        <v>371</v>
       </c>
       <c r="B58" t="s" s="2">
-        <v>372</v>
+        <v>371</v>
       </c>
       <c r="C58" s="2"/>
       <c r="D58" t="s" s="2">
@@ -9183,16 +9178,16 @@
         <v>82</v>
       </c>
       <c r="K58" t="s" s="2">
+        <v>372</v>
+      </c>
+      <c r="L58" t="s" s="2">
         <v>373</v>
       </c>
-      <c r="L58" t="s" s="2">
+      <c r="M58" t="s" s="2">
         <v>374</v>
       </c>
-      <c r="M58" t="s" s="2">
+      <c r="N58" t="s" s="2">
         <v>375</v>
-      </c>
-      <c r="N58" t="s" s="2">
-        <v>376</v>
       </c>
       <c r="O58" s="2"/>
       <c r="P58" t="s" s="2">
@@ -9242,7 +9237,7 @@
         <v>82</v>
       </c>
       <c r="AF58" t="s" s="2">
-        <v>372</v>
+        <v>371</v>
       </c>
       <c r="AG58" t="s" s="2">
         <v>80</v>
@@ -9257,16 +9252,16 @@
         <v>103</v>
       </c>
       <c r="AK58" t="s" s="2">
+        <v>376</v>
+      </c>
+      <c r="AL58" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM58" t="s" s="2">
         <v>377</v>
       </c>
-      <c r="AL58" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AM58" t="s" s="2">
-        <v>378</v>
-      </c>
       <c r="AN58" t="s" s="2">
-        <v>370</v>
+        <v>369</v>
       </c>
       <c r="AO58" t="s" s="2">
         <v>82</v>
@@ -9274,10 +9269,10 @@
     </row>
     <row r="59">
       <c r="A59" t="s" s="2">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="B59" t="s" s="2">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="C59" s="2"/>
       <c r="D59" t="s" s="2">
@@ -9300,13 +9295,13 @@
         <v>92</v>
       </c>
       <c r="K59" t="s" s="2">
+        <v>379</v>
+      </c>
+      <c r="L59" t="s" s="2">
         <v>380</v>
       </c>
-      <c r="L59" t="s" s="2">
+      <c r="M59" t="s" s="2">
         <v>381</v>
-      </c>
-      <c r="M59" t="s" s="2">
-        <v>382</v>
       </c>
       <c r="N59" s="2"/>
       <c r="O59" s="2"/>
@@ -9357,7 +9352,7 @@
         <v>82</v>
       </c>
       <c r="AF59" t="s" s="2">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="AG59" t="s" s="2">
         <v>80</v>
@@ -9372,27 +9367,27 @@
         <v>103</v>
       </c>
       <c r="AK59" t="s" s="2">
+        <v>382</v>
+      </c>
+      <c r="AL59" t="s" s="2">
         <v>383</v>
       </c>
-      <c r="AL59" t="s" s="2">
+      <c r="AM59" t="s" s="2">
         <v>384</v>
       </c>
-      <c r="AM59" t="s" s="2">
+      <c r="AN59" t="s" s="2">
         <v>385</v>
       </c>
-      <c r="AN59" t="s" s="2">
+      <c r="AO59" t="s" s="2">
         <v>386</v>
-      </c>
-      <c r="AO59" t="s" s="2">
-        <v>387</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="s" s="2">
-        <v>388</v>
+        <v>387</v>
       </c>
       <c r="B60" t="s" s="2">
-        <v>388</v>
+        <v>387</v>
       </c>
       <c r="C60" s="2"/>
       <c r="D60" t="s" s="2">
@@ -9415,16 +9410,16 @@
         <v>92</v>
       </c>
       <c r="K60" t="s" s="2">
+        <v>388</v>
+      </c>
+      <c r="L60" t="s" s="2">
         <v>389</v>
       </c>
-      <c r="L60" t="s" s="2">
+      <c r="M60" t="s" s="2">
         <v>390</v>
       </c>
-      <c r="M60" t="s" s="2">
-        <v>391</v>
-      </c>
       <c r="N60" t="s" s="2">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="O60" s="2"/>
       <c r="P60" t="s" s="2">
@@ -9474,7 +9469,7 @@
         <v>82</v>
       </c>
       <c r="AF60" t="s" s="2">
-        <v>388</v>
+        <v>387</v>
       </c>
       <c r="AG60" t="s" s="2">
         <v>80</v>
@@ -9489,16 +9484,16 @@
         <v>103</v>
       </c>
       <c r="AK60" t="s" s="2">
+        <v>391</v>
+      </c>
+      <c r="AL60" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM60" t="s" s="2">
+        <v>359</v>
+      </c>
+      <c r="AN60" t="s" s="2">
         <v>392</v>
-      </c>
-      <c r="AL60" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AM60" t="s" s="2">
-        <v>360</v>
-      </c>
-      <c r="AN60" t="s" s="2">
-        <v>393</v>
       </c>
       <c r="AO60" t="s" s="2">
         <v>82</v>
@@ -9506,10 +9501,10 @@
     </row>
     <row r="61">
       <c r="A61" t="s" s="2">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="B61" t="s" s="2">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="C61" s="2"/>
       <c r="D61" t="s" s="2">
@@ -9532,16 +9527,16 @@
         <v>82</v>
       </c>
       <c r="K61" t="s" s="2">
+        <v>394</v>
+      </c>
+      <c r="L61" t="s" s="2">
         <v>395</v>
       </c>
-      <c r="L61" t="s" s="2">
+      <c r="M61" t="s" s="2">
         <v>396</v>
       </c>
-      <c r="M61" t="s" s="2">
-        <v>397</v>
-      </c>
       <c r="N61" t="s" s="2">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="O61" s="2"/>
       <c r="P61" t="s" s="2">
@@ -9591,7 +9586,7 @@
         <v>82</v>
       </c>
       <c r="AF61" t="s" s="2">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="AG61" t="s" s="2">
         <v>80</v>
@@ -9606,16 +9601,16 @@
         <v>103</v>
       </c>
       <c r="AK61" t="s" s="2">
+        <v>397</v>
+      </c>
+      <c r="AL61" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM61" t="s" s="2">
         <v>398</v>
       </c>
-      <c r="AL61" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AM61" t="s" s="2">
+      <c r="AN61" t="s" s="2">
         <v>399</v>
-      </c>
-      <c r="AN61" t="s" s="2">
-        <v>400</v>
       </c>
       <c r="AO61" t="s" s="2">
         <v>82</v>
@@ -9623,10 +9618,10 @@
     </row>
     <row r="62">
       <c r="A62" t="s" s="2">
-        <v>401</v>
+        <v>400</v>
       </c>
       <c r="B62" t="s" s="2">
-        <v>401</v>
+        <v>400</v>
       </c>
       <c r="C62" s="2"/>
       <c r="D62" t="s" s="2">
@@ -9652,13 +9647,13 @@
         <v>193</v>
       </c>
       <c r="L62" t="s" s="2">
+        <v>401</v>
+      </c>
+      <c r="M62" t="s" s="2">
         <v>402</v>
       </c>
-      <c r="M62" t="s" s="2">
+      <c r="N62" t="s" s="2">
         <v>403</v>
-      </c>
-      <c r="N62" t="s" s="2">
-        <v>404</v>
       </c>
       <c r="O62" s="2"/>
       <c r="P62" t="s" s="2">
@@ -9688,7 +9683,7 @@
       </c>
       <c r="Y62" s="2"/>
       <c r="Z62" t="s" s="2">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="AA62" t="s" s="2">
         <v>82</v>
@@ -9706,7 +9701,7 @@
         <v>82</v>
       </c>
       <c r="AF62" t="s" s="2">
-        <v>401</v>
+        <v>400</v>
       </c>
       <c r="AG62" t="s" s="2">
         <v>80</v>
@@ -9721,13 +9716,13 @@
         <v>103</v>
       </c>
       <c r="AK62" t="s" s="2">
+        <v>405</v>
+      </c>
+      <c r="AL62" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM62" t="s" s="2">
         <v>406</v>
-      </c>
-      <c r="AL62" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AM62" t="s" s="2">
-        <v>407</v>
       </c>
       <c r="AN62" t="s" s="2">
         <v>82</v>
@@ -9738,10 +9733,10 @@
     </row>
     <row r="63">
       <c r="A63" t="s" s="2">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="B63" t="s" s="2">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="C63" s="2"/>
       <c r="D63" t="s" s="2">
@@ -9764,16 +9759,16 @@
         <v>82</v>
       </c>
       <c r="K63" t="s" s="2">
+        <v>408</v>
+      </c>
+      <c r="L63" t="s" s="2">
         <v>409</v>
       </c>
-      <c r="L63" t="s" s="2">
+      <c r="M63" t="s" s="2">
         <v>410</v>
       </c>
-      <c r="M63" t="s" s="2">
-        <v>411</v>
-      </c>
       <c r="N63" t="s" s="2">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="O63" s="2"/>
       <c r="P63" t="s" s="2">
@@ -9823,7 +9818,7 @@
         <v>82</v>
       </c>
       <c r="AF63" t="s" s="2">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="AG63" t="s" s="2">
         <v>80</v>
@@ -9844,10 +9839,10 @@
         <v>82</v>
       </c>
       <c r="AM63" t="s" s="2">
+        <v>411</v>
+      </c>
+      <c r="AN63" t="s" s="2">
         <v>412</v>
-      </c>
-      <c r="AN63" t="s" s="2">
-        <v>413</v>
       </c>
       <c r="AO63" t="s" s="2">
         <v>82</v>
@@ -9855,10 +9850,10 @@
     </row>
     <row r="64">
       <c r="A64" t="s" s="2">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="B64" t="s" s="2">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="C64" s="2"/>
       <c r="D64" t="s" s="2">
@@ -9884,13 +9879,13 @@
         <v>193</v>
       </c>
       <c r="L64" t="s" s="2">
+        <v>414</v>
+      </c>
+      <c r="M64" t="s" s="2">
         <v>415</v>
       </c>
-      <c r="M64" t="s" s="2">
+      <c r="N64" t="s" s="2">
         <v>416</v>
-      </c>
-      <c r="N64" t="s" s="2">
-        <v>417</v>
       </c>
       <c r="O64" s="2"/>
       <c r="P64" t="s" s="2">
@@ -9919,11 +9914,11 @@
         <v>301</v>
       </c>
       <c r="Y64" t="s" s="2">
+        <v>417</v>
+      </c>
+      <c r="Z64" t="s" s="2">
         <v>418</v>
       </c>
-      <c r="Z64" t="s" s="2">
-        <v>419</v>
-      </c>
       <c r="AA64" t="s" s="2">
         <v>82</v>
       </c>
@@ -9940,7 +9935,7 @@
         <v>82</v>
       </c>
       <c r="AF64" t="s" s="2">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="AG64" t="s" s="2">
         <v>80</v>
@@ -9955,27 +9950,27 @@
         <v>103</v>
       </c>
       <c r="AK64" t="s" s="2">
+        <v>419</v>
+      </c>
+      <c r="AL64" t="s" s="2">
         <v>420</v>
       </c>
-      <c r="AL64" t="s" s="2">
+      <c r="AM64" t="s" s="2">
         <v>421</v>
       </c>
-      <c r="AM64" t="s" s="2">
+      <c r="AN64" t="s" s="2">
         <v>422</v>
       </c>
-      <c r="AN64" t="s" s="2">
+      <c r="AO64" t="s" s="2">
         <v>423</v>
-      </c>
-      <c r="AO64" t="s" s="2">
-        <v>424</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="s" s="2">
-        <v>425</v>
+        <v>424</v>
       </c>
       <c r="B65" t="s" s="2">
-        <v>425</v>
+        <v>424</v>
       </c>
       <c r="C65" s="2"/>
       <c r="D65" t="s" s="2">
@@ -9998,16 +9993,16 @@
         <v>82</v>
       </c>
       <c r="K65" t="s" s="2">
+        <v>425</v>
+      </c>
+      <c r="L65" t="s" s="2">
         <v>426</v>
       </c>
-      <c r="L65" t="s" s="2">
+      <c r="M65" t="s" s="2">
         <v>427</v>
       </c>
-      <c r="M65" t="s" s="2">
+      <c r="N65" t="s" s="2">
         <v>428</v>
-      </c>
-      <c r="N65" t="s" s="2">
-        <v>429</v>
       </c>
       <c r="O65" s="2"/>
       <c r="P65" t="s" s="2">
@@ -10057,7 +10052,7 @@
         <v>82</v>
       </c>
       <c r="AF65" t="s" s="2">
-        <v>425</v>
+        <v>424</v>
       </c>
       <c r="AG65" t="s" s="2">
         <v>80</v>
@@ -10072,16 +10067,16 @@
         <v>103</v>
       </c>
       <c r="AK65" t="s" s="2">
-        <v>430</v>
+        <v>429</v>
       </c>
       <c r="AL65" t="s" s="2">
         <v>295</v>
       </c>
       <c r="AM65" t="s" s="2">
-        <v>431</v>
+        <v>430</v>
       </c>
       <c r="AN65" t="s" s="2">
-        <v>423</v>
+        <v>422</v>
       </c>
       <c r="AO65" t="s" s="2">
         <v>82</v>
@@ -10089,10 +10084,10 @@
     </row>
     <row r="66">
       <c r="A66" t="s" s="2">
-        <v>432</v>
+        <v>431</v>
       </c>
       <c r="B66" t="s" s="2">
-        <v>432</v>
+        <v>431</v>
       </c>
       <c r="C66" s="2"/>
       <c r="D66" t="s" s="2">
@@ -10115,16 +10110,16 @@
         <v>92</v>
       </c>
       <c r="K66" t="s" s="2">
+        <v>432</v>
+      </c>
+      <c r="L66" t="s" s="2">
         <v>433</v>
       </c>
-      <c r="L66" t="s" s="2">
+      <c r="M66" t="s" s="2">
         <v>434</v>
       </c>
-      <c r="M66" t="s" s="2">
+      <c r="N66" t="s" s="2">
         <v>435</v>
-      </c>
-      <c r="N66" t="s" s="2">
-        <v>436</v>
       </c>
       <c r="O66" s="2"/>
       <c r="P66" t="s" s="2">
@@ -10174,7 +10169,7 @@
         <v>82</v>
       </c>
       <c r="AF66" t="s" s="2">
-        <v>432</v>
+        <v>431</v>
       </c>
       <c r="AG66" t="s" s="2">
         <v>80</v>
@@ -10189,13 +10184,13 @@
         <v>103</v>
       </c>
       <c r="AK66" t="s" s="2">
+        <v>436</v>
+      </c>
+      <c r="AL66" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM66" t="s" s="2">
         <v>437</v>
-      </c>
-      <c r="AL66" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AM66" t="s" s="2">
-        <v>438</v>
       </c>
       <c r="AN66" t="s" s="2">
         <v>82</v>
@@ -10206,10 +10201,10 @@
     </row>
     <row r="67">
       <c r="A67" t="s" s="2">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="B67" t="s" s="2">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="C67" s="2"/>
       <c r="D67" t="s" s="2">
@@ -10235,13 +10230,13 @@
         <v>105</v>
       </c>
       <c r="L67" t="s" s="2">
+        <v>439</v>
+      </c>
+      <c r="M67" t="s" s="2">
+        <v>434</v>
+      </c>
+      <c r="N67" t="s" s="2">
         <v>440</v>
-      </c>
-      <c r="M67" t="s" s="2">
-        <v>435</v>
-      </c>
-      <c r="N67" t="s" s="2">
-        <v>441</v>
       </c>
       <c r="O67" s="2"/>
       <c r="P67" t="s" s="2">
@@ -10291,7 +10286,7 @@
         <v>82</v>
       </c>
       <c r="AF67" t="s" s="2">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="AG67" t="s" s="2">
         <v>80</v>
@@ -10312,7 +10307,7 @@
         <v>82</v>
       </c>
       <c r="AM67" t="s" s="2">
-        <v>438</v>
+        <v>437</v>
       </c>
       <c r="AN67" t="s" s="2">
         <v>82</v>
@@ -10323,10 +10318,10 @@
     </row>
     <row r="68">
       <c r="A68" t="s" s="2">
-        <v>442</v>
+        <v>441</v>
       </c>
       <c r="B68" t="s" s="2">
-        <v>442</v>
+        <v>441</v>
       </c>
       <c r="C68" s="2"/>
       <c r="D68" t="s" s="2">
@@ -10349,16 +10344,16 @@
         <v>92</v>
       </c>
       <c r="K68" t="s" s="2">
+        <v>442</v>
+      </c>
+      <c r="L68" t="s" s="2">
         <v>443</v>
       </c>
-      <c r="L68" t="s" s="2">
+      <c r="M68" t="s" s="2">
         <v>444</v>
       </c>
-      <c r="M68" t="s" s="2">
-        <v>445</v>
-      </c>
       <c r="N68" t="s" s="2">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="O68" s="2"/>
       <c r="P68" t="s" s="2">
@@ -10408,7 +10403,7 @@
         <v>82</v>
       </c>
       <c r="AF68" t="s" s="2">
-        <v>442</v>
+        <v>441</v>
       </c>
       <c r="AG68" t="s" s="2">
         <v>80</v>
@@ -10423,13 +10418,13 @@
         <v>103</v>
       </c>
       <c r="AK68" t="s" s="2">
+        <v>445</v>
+      </c>
+      <c r="AL68" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM68" t="s" s="2">
         <v>446</v>
-      </c>
-      <c r="AL68" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AM68" t="s" s="2">
-        <v>447</v>
       </c>
       <c r="AN68" t="s" s="2">
         <v>82</v>
@@ -10440,10 +10435,10 @@
     </row>
     <row r="69">
       <c r="A69" t="s" s="2">
-        <v>448</v>
+        <v>447</v>
       </c>
       <c r="B69" t="s" s="2">
-        <v>448</v>
+        <v>447</v>
       </c>
       <c r="C69" s="2"/>
       <c r="D69" t="s" s="2">
@@ -10469,14 +10464,14 @@
         <v>150</v>
       </c>
       <c r="L69" t="s" s="2">
+        <v>448</v>
+      </c>
+      <c r="M69" t="s" s="2">
         <v>449</v>
-      </c>
-      <c r="M69" t="s" s="2">
-        <v>450</v>
       </c>
       <c r="N69" s="2"/>
       <c r="O69" t="s" s="2">
-        <v>451</v>
+        <v>450</v>
       </c>
       <c r="P69" t="s" s="2">
         <v>82</v>
@@ -10525,7 +10520,7 @@
         <v>82</v>
       </c>
       <c r="AF69" t="s" s="2">
-        <v>448</v>
+        <v>447</v>
       </c>
       <c r="AG69" t="s" s="2">
         <v>80</v>
@@ -10540,13 +10535,13 @@
         <v>103</v>
       </c>
       <c r="AK69" t="s" s="2">
+        <v>451</v>
+      </c>
+      <c r="AL69" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM69" t="s" s="2">
         <v>452</v>
-      </c>
-      <c r="AL69" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AM69" t="s" s="2">
-        <v>453</v>
       </c>
       <c r="AN69" t="s" s="2">
         <v>82</v>
@@ -10557,10 +10552,10 @@
     </row>
     <row r="70">
       <c r="A70" t="s" s="2">
-        <v>454</v>
+        <v>453</v>
       </c>
       <c r="B70" t="s" s="2">
-        <v>454</v>
+        <v>453</v>
       </c>
       <c r="C70" s="2"/>
       <c r="D70" t="s" s="2">
@@ -10586,13 +10581,13 @@
         <v>193</v>
       </c>
       <c r="L70" t="s" s="2">
+        <v>454</v>
+      </c>
+      <c r="M70" t="s" s="2">
         <v>455</v>
       </c>
-      <c r="M70" t="s" s="2">
+      <c r="N70" t="s" s="2">
         <v>456</v>
-      </c>
-      <c r="N70" t="s" s="2">
-        <v>457</v>
       </c>
       <c r="O70" s="2"/>
       <c r="P70" t="s" s="2">
@@ -10621,11 +10616,11 @@
         <v>301</v>
       </c>
       <c r="Y70" t="s" s="2">
+        <v>457</v>
+      </c>
+      <c r="Z70" t="s" s="2">
         <v>458</v>
       </c>
-      <c r="Z70" t="s" s="2">
-        <v>459</v>
-      </c>
       <c r="AA70" t="s" s="2">
         <v>82</v>
       </c>
@@ -10642,7 +10637,7 @@
         <v>82</v>
       </c>
       <c r="AF70" t="s" s="2">
-        <v>454</v>
+        <v>453</v>
       </c>
       <c r="AG70" t="s" s="2">
         <v>80</v>
@@ -10663,7 +10658,7 @@
         <v>82</v>
       </c>
       <c r="AM70" t="s" s="2">
-        <v>460</v>
+        <v>459</v>
       </c>
       <c r="AN70" t="s" s="2">
         <v>82</v>
@@ -10674,10 +10669,10 @@
     </row>
     <row r="71">
       <c r="A71" t="s" s="2">
-        <v>461</v>
+        <v>460</v>
       </c>
       <c r="B71" t="s" s="2">
-        <v>461</v>
+        <v>460</v>
       </c>
       <c r="C71" s="2"/>
       <c r="D71" t="s" s="2">
@@ -10700,16 +10695,16 @@
         <v>82</v>
       </c>
       <c r="K71" t="s" s="2">
+        <v>461</v>
+      </c>
+      <c r="L71" t="s" s="2">
         <v>462</v>
       </c>
-      <c r="L71" t="s" s="2">
+      <c r="M71" t="s" s="2">
         <v>463</v>
       </c>
-      <c r="M71" t="s" s="2">
-        <v>464</v>
-      </c>
       <c r="N71" t="s" s="2">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="O71" s="2"/>
       <c r="P71" t="s" s="2">
@@ -10759,7 +10754,7 @@
         <v>82</v>
       </c>
       <c r="AF71" t="s" s="2">
-        <v>461</v>
+        <v>460</v>
       </c>
       <c r="AG71" t="s" s="2">
         <v>80</v>
@@ -10774,13 +10769,13 @@
         <v>103</v>
       </c>
       <c r="AK71" t="s" s="2">
+        <v>464</v>
+      </c>
+      <c r="AL71" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM71" t="s" s="2">
         <v>465</v>
-      </c>
-      <c r="AL71" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AM71" t="s" s="2">
-        <v>466</v>
       </c>
       <c r="AN71" t="s" s="2">
         <v>82</v>
@@ -10791,10 +10786,10 @@
     </row>
     <row r="72">
       <c r="A72" t="s" s="2">
-        <v>467</v>
+        <v>466</v>
       </c>
       <c r="B72" t="s" s="2">
-        <v>467</v>
+        <v>466</v>
       </c>
       <c r="C72" s="2"/>
       <c r="D72" t="s" s="2">
@@ -10817,16 +10812,16 @@
         <v>82</v>
       </c>
       <c r="K72" t="s" s="2">
+        <v>467</v>
+      </c>
+      <c r="L72" t="s" s="2">
         <v>468</v>
       </c>
-      <c r="L72" t="s" s="2">
+      <c r="M72" t="s" s="2">
         <v>469</v>
       </c>
-      <c r="M72" t="s" s="2">
+      <c r="N72" t="s" s="2">
         <v>470</v>
-      </c>
-      <c r="N72" t="s" s="2">
-        <v>471</v>
       </c>
       <c r="O72" s="2"/>
       <c r="P72" t="s" s="2">
@@ -10876,7 +10871,7 @@
         <v>82</v>
       </c>
       <c r="AF72" t="s" s="2">
-        <v>467</v>
+        <v>466</v>
       </c>
       <c r="AG72" t="s" s="2">
         <v>80</v>
@@ -10891,13 +10886,13 @@
         <v>103</v>
       </c>
       <c r="AK72" t="s" s="2">
+        <v>471</v>
+      </c>
+      <c r="AL72" t="s" s="2">
         <v>472</v>
       </c>
-      <c r="AL72" t="s" s="2">
+      <c r="AM72" t="s" s="2">
         <v>473</v>
-      </c>
-      <c r="AM72" t="s" s="2">
-        <v>474</v>
       </c>
       <c r="AN72" t="s" s="2">
         <v>82</v>
@@ -10908,10 +10903,10 @@
     </row>
     <row r="73">
       <c r="A73" t="s" s="2">
-        <v>475</v>
+        <v>474</v>
       </c>
       <c r="B73" t="s" s="2">
-        <v>475</v>
+        <v>474</v>
       </c>
       <c r="C73" s="2"/>
       <c r="D73" t="s" s="2">
@@ -10934,16 +10929,16 @@
         <v>82</v>
       </c>
       <c r="K73" t="s" s="2">
+        <v>475</v>
+      </c>
+      <c r="L73" t="s" s="2">
         <v>476</v>
       </c>
-      <c r="L73" t="s" s="2">
+      <c r="M73" t="s" s="2">
         <v>477</v>
       </c>
-      <c r="M73" t="s" s="2">
+      <c r="N73" t="s" s="2">
         <v>478</v>
-      </c>
-      <c r="N73" t="s" s="2">
-        <v>479</v>
       </c>
       <c r="O73" s="2"/>
       <c r="P73" t="s" s="2">
@@ -10993,7 +10988,7 @@
         <v>82</v>
       </c>
       <c r="AF73" t="s" s="2">
-        <v>475</v>
+        <v>474</v>
       </c>
       <c r="AG73" t="s" s="2">
         <v>80</v>
@@ -11008,13 +11003,13 @@
         <v>103</v>
       </c>
       <c r="AK73" t="s" s="2">
+        <v>479</v>
+      </c>
+      <c r="AL73" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM73" t="s" s="2">
         <v>480</v>
-      </c>
-      <c r="AL73" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AM73" t="s" s="2">
-        <v>481</v>
       </c>
       <c r="AN73" t="s" s="2">
         <v>82</v>
@@ -11025,10 +11020,10 @@
     </row>
     <row r="74">
       <c r="A74" t="s" s="2">
-        <v>482</v>
+        <v>481</v>
       </c>
       <c r="B74" t="s" s="2">
-        <v>482</v>
+        <v>481</v>
       </c>
       <c r="C74" s="2"/>
       <c r="D74" t="s" s="2">
@@ -11051,13 +11046,13 @@
         <v>82</v>
       </c>
       <c r="K74" t="s" s="2">
+        <v>482</v>
+      </c>
+      <c r="L74" t="s" s="2">
         <v>483</v>
       </c>
-      <c r="L74" t="s" s="2">
+      <c r="M74" t="s" s="2">
         <v>484</v>
-      </c>
-      <c r="M74" t="s" s="2">
-        <v>485</v>
       </c>
       <c r="N74" s="2"/>
       <c r="O74" s="2"/>
@@ -11108,7 +11103,7 @@
         <v>82</v>
       </c>
       <c r="AF74" t="s" s="2">
-        <v>482</v>
+        <v>481</v>
       </c>
       <c r="AG74" t="s" s="2">
         <v>80</v>
@@ -11126,10 +11121,10 @@
         <v>82</v>
       </c>
       <c r="AL74" t="s" s="2">
+        <v>485</v>
+      </c>
+      <c r="AM74" t="s" s="2">
         <v>486</v>
-      </c>
-      <c r="AM74" t="s" s="2">
-        <v>487</v>
       </c>
       <c r="AN74" t="s" s="2">
         <v>82</v>
@@ -11140,10 +11135,10 @@
     </row>
     <row r="75">
       <c r="A75" t="s" s="2">
-        <v>488</v>
+        <v>487</v>
       </c>
       <c r="B75" t="s" s="2">
-        <v>488</v>
+        <v>487</v>
       </c>
       <c r="C75" s="2"/>
       <c r="D75" t="s" s="2">
@@ -11169,10 +11164,10 @@
         <v>169</v>
       </c>
       <c r="L75" t="s" s="2">
+        <v>488</v>
+      </c>
+      <c r="M75" t="s" s="2">
         <v>489</v>
-      </c>
-      <c r="M75" t="s" s="2">
-        <v>490</v>
       </c>
       <c r="N75" s="2"/>
       <c r="O75" s="2"/>
@@ -11255,10 +11250,10 @@
     </row>
     <row r="76">
       <c r="A76" t="s" s="2">
-        <v>491</v>
+        <v>490</v>
       </c>
       <c r="B76" t="s" s="2">
-        <v>491</v>
+        <v>490</v>
       </c>
       <c r="C76" s="2"/>
       <c r="D76" t="s" s="2">
@@ -11284,10 +11279,10 @@
         <v>137</v>
       </c>
       <c r="L76" t="s" s="2">
+        <v>491</v>
+      </c>
+      <c r="M76" t="s" s="2">
         <v>492</v>
-      </c>
-      <c r="M76" t="s" s="2">
-        <v>493</v>
       </c>
       <c r="N76" s="2"/>
       <c r="O76" s="2"/>
@@ -11368,13 +11363,13 @@
     </row>
     <row r="77">
       <c r="A77" t="s" s="2">
+        <v>493</v>
+      </c>
+      <c r="B77" t="s" s="2">
+        <v>490</v>
+      </c>
+      <c r="C77" t="s" s="2">
         <v>494</v>
-      </c>
-      <c r="B77" t="s" s="2">
-        <v>491</v>
-      </c>
-      <c r="C77" t="s" s="2">
-        <v>495</v>
       </c>
       <c r="D77" t="s" s="2">
         <v>82</v>
@@ -11396,13 +11391,13 @@
         <v>82</v>
       </c>
       <c r="K77" t="s" s="2">
+        <v>495</v>
+      </c>
+      <c r="L77" t="s" s="2">
         <v>496</v>
       </c>
-      <c r="L77" t="s" s="2">
+      <c r="M77" t="s" s="2">
         <v>497</v>
-      </c>
-      <c r="M77" t="s" s="2">
-        <v>498</v>
       </c>
       <c r="N77" s="2"/>
       <c r="O77" s="2"/>
@@ -11462,7 +11457,7 @@
         <v>81</v>
       </c>
       <c r="AI77" t="s" s="2">
-        <v>499</v>
+        <v>498</v>
       </c>
       <c r="AJ77" t="s" s="2">
         <v>142</v>
@@ -11485,13 +11480,13 @@
     </row>
     <row r="78">
       <c r="A78" t="s" s="2">
+        <v>499</v>
+      </c>
+      <c r="B78" t="s" s="2">
+        <v>490</v>
+      </c>
+      <c r="C78" t="s" s="2">
         <v>500</v>
-      </c>
-      <c r="B78" t="s" s="2">
-        <v>491</v>
-      </c>
-      <c r="C78" t="s" s="2">
-        <v>501</v>
       </c>
       <c r="D78" t="s" s="2">
         <v>82</v>
@@ -11513,13 +11508,13 @@
         <v>82</v>
       </c>
       <c r="K78" t="s" s="2">
+        <v>501</v>
+      </c>
+      <c r="L78" t="s" s="2">
         <v>502</v>
       </c>
-      <c r="L78" t="s" s="2">
+      <c r="M78" t="s" s="2">
         <v>503</v>
-      </c>
-      <c r="M78" t="s" s="2">
-        <v>504</v>
       </c>
       <c r="N78" s="2"/>
       <c r="O78" s="2"/>
@@ -11579,7 +11574,7 @@
         <v>81</v>
       </c>
       <c r="AI78" t="s" s="2">
-        <v>499</v>
+        <v>498</v>
       </c>
       <c r="AJ78" t="s" s="2">
         <v>142</v>
@@ -11602,14 +11597,14 @@
     </row>
     <row r="79">
       <c r="A79" t="s" s="2">
-        <v>505</v>
+        <v>504</v>
       </c>
       <c r="B79" t="s" s="2">
-        <v>505</v>
+        <v>504</v>
       </c>
       <c r="C79" s="2"/>
       <c r="D79" t="s" s="2">
-        <v>506</v>
+        <v>505</v>
       </c>
       <c r="E79" s="2"/>
       <c r="F79" t="s" s="2">
@@ -11631,10 +11626,10 @@
         <v>137</v>
       </c>
       <c r="L79" t="s" s="2">
+        <v>506</v>
+      </c>
+      <c r="M79" t="s" s="2">
         <v>507</v>
-      </c>
-      <c r="M79" t="s" s="2">
-        <v>508</v>
       </c>
       <c r="N79" t="s" s="2">
         <v>140</v>
@@ -11689,7 +11684,7 @@
         <v>82</v>
       </c>
       <c r="AF79" t="s" s="2">
-        <v>509</v>
+        <v>508</v>
       </c>
       <c r="AG79" t="s" s="2">
         <v>80</v>
@@ -11721,10 +11716,10 @@
     </row>
     <row r="80">
       <c r="A80" t="s" s="2">
-        <v>510</v>
+        <v>509</v>
       </c>
       <c r="B80" t="s" s="2">
-        <v>510</v>
+        <v>509</v>
       </c>
       <c r="C80" s="2"/>
       <c r="D80" t="s" s="2">
@@ -11747,16 +11742,16 @@
         <v>82</v>
       </c>
       <c r="K80" t="s" s="2">
-        <v>483</v>
+        <v>482</v>
       </c>
       <c r="L80" t="s" s="2">
+        <v>510</v>
+      </c>
+      <c r="M80" t="s" s="2">
         <v>511</v>
       </c>
-      <c r="M80" t="s" s="2">
+      <c r="N80" t="s" s="2">
         <v>512</v>
-      </c>
-      <c r="N80" t="s" s="2">
-        <v>513</v>
       </c>
       <c r="O80" s="2"/>
       <c r="P80" t="s" s="2">
@@ -11806,7 +11801,7 @@
         <v>82</v>
       </c>
       <c r="AF80" t="s" s="2">
-        <v>510</v>
+        <v>509</v>
       </c>
       <c r="AG80" t="s" s="2">
         <v>80</v>
@@ -11827,7 +11822,7 @@
         <v>82</v>
       </c>
       <c r="AM80" t="s" s="2">
-        <v>514</v>
+        <v>513</v>
       </c>
       <c r="AN80" t="s" s="2">
         <v>82</v>
@@ -11838,10 +11833,10 @@
     </row>
     <row r="81">
       <c r="A81" t="s" s="2">
-        <v>515</v>
+        <v>514</v>
       </c>
       <c r="B81" t="s" s="2">
-        <v>515</v>
+        <v>514</v>
       </c>
       <c r="C81" s="2"/>
       <c r="D81" t="s" s="2">
@@ -11953,10 +11948,10 @@
     </row>
     <row r="82">
       <c r="A82" t="s" s="2">
-        <v>516</v>
+        <v>515</v>
       </c>
       <c r="B82" t="s" s="2">
-        <v>516</v>
+        <v>515</v>
       </c>
       <c r="C82" s="2"/>
       <c r="D82" t="s" s="2">
@@ -12070,14 +12065,14 @@
     </row>
     <row r="83">
       <c r="A83" t="s" s="2">
-        <v>517</v>
+        <v>516</v>
       </c>
       <c r="B83" t="s" s="2">
-        <v>517</v>
+        <v>516</v>
       </c>
       <c r="C83" s="2"/>
       <c r="D83" t="s" s="2">
-        <v>506</v>
+        <v>505</v>
       </c>
       <c r="E83" s="2"/>
       <c r="F83" t="s" s="2">
@@ -12099,10 +12094,10 @@
         <v>137</v>
       </c>
       <c r="L83" t="s" s="2">
+        <v>506</v>
+      </c>
+      <c r="M83" t="s" s="2">
         <v>507</v>
-      </c>
-      <c r="M83" t="s" s="2">
-        <v>508</v>
       </c>
       <c r="N83" t="s" s="2">
         <v>140</v>
@@ -12157,7 +12152,7 @@
         <v>82</v>
       </c>
       <c r="AF83" t="s" s="2">
-        <v>509</v>
+        <v>508</v>
       </c>
       <c r="AG83" t="s" s="2">
         <v>80</v>
@@ -12189,10 +12184,10 @@
     </row>
     <row r="84">
       <c r="A84" t="s" s="2">
-        <v>518</v>
+        <v>517</v>
       </c>
       <c r="B84" t="s" s="2">
-        <v>518</v>
+        <v>517</v>
       </c>
       <c r="C84" s="2"/>
       <c r="D84" t="s" s="2">
@@ -12215,16 +12210,16 @@
         <v>82</v>
       </c>
       <c r="K84" t="s" s="2">
+        <v>518</v>
+      </c>
+      <c r="L84" t="s" s="2">
         <v>519</v>
       </c>
-      <c r="L84" t="s" s="2">
+      <c r="M84" t="s" s="2">
         <v>520</v>
       </c>
-      <c r="M84" t="s" s="2">
+      <c r="N84" t="s" s="2">
         <v>521</v>
-      </c>
-      <c r="N84" t="s" s="2">
-        <v>522</v>
       </c>
       <c r="O84" s="2"/>
       <c r="P84" t="s" s="2">
@@ -12274,7 +12269,7 @@
         <v>82</v>
       </c>
       <c r="AF84" t="s" s="2">
-        <v>518</v>
+        <v>517</v>
       </c>
       <c r="AG84" t="s" s="2">
         <v>80</v>
@@ -12295,7 +12290,7 @@
         <v>82</v>
       </c>
       <c r="AM84" t="s" s="2">
-        <v>523</v>
+        <v>522</v>
       </c>
       <c r="AN84" t="s" s="2">
         <v>82</v>
@@ -12306,10 +12301,10 @@
     </row>
     <row r="85">
       <c r="A85" t="s" s="2">
-        <v>524</v>
+        <v>523</v>
       </c>
       <c r="B85" t="s" s="2">
-        <v>524</v>
+        <v>523</v>
       </c>
       <c r="C85" s="2"/>
       <c r="D85" t="s" s="2">
@@ -12332,16 +12327,16 @@
         <v>82</v>
       </c>
       <c r="K85" t="s" s="2">
+        <v>524</v>
+      </c>
+      <c r="L85" t="s" s="2">
         <v>525</v>
       </c>
-      <c r="L85" t="s" s="2">
+      <c r="M85" t="s" s="2">
         <v>526</v>
       </c>
-      <c r="M85" t="s" s="2">
-        <v>527</v>
-      </c>
       <c r="N85" t="s" s="2">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="O85" s="2"/>
       <c r="P85" t="s" s="2">
@@ -12391,7 +12386,7 @@
         <v>82</v>
       </c>
       <c r="AF85" t="s" s="2">
-        <v>524</v>
+        <v>523</v>
       </c>
       <c r="AG85" t="s" s="2">
         <v>80</v>
@@ -12412,7 +12407,7 @@
         <v>82</v>
       </c>
       <c r="AM85" t="s" s="2">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="AN85" t="s" s="2">
         <v>82</v>
@@ -12423,10 +12418,10 @@
     </row>
     <row r="86">
       <c r="A86" t="s" s="2">
-        <v>529</v>
+        <v>528</v>
       </c>
       <c r="B86" t="s" s="2">
-        <v>529</v>
+        <v>528</v>
       </c>
       <c r="C86" s="2"/>
       <c r="D86" t="s" s="2">
@@ -12449,16 +12444,16 @@
         <v>82</v>
       </c>
       <c r="K86" t="s" s="2">
-        <v>525</v>
+        <v>524</v>
       </c>
       <c r="L86" t="s" s="2">
+        <v>529</v>
+      </c>
+      <c r="M86" t="s" s="2">
         <v>530</v>
       </c>
-      <c r="M86" t="s" s="2">
-        <v>531</v>
-      </c>
       <c r="N86" t="s" s="2">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="O86" s="2"/>
       <c r="P86" t="s" s="2">
@@ -12508,7 +12503,7 @@
         <v>82</v>
       </c>
       <c r="AF86" t="s" s="2">
-        <v>529</v>
+        <v>528</v>
       </c>
       <c r="AG86" t="s" s="2">
         <v>80</v>
@@ -12529,7 +12524,7 @@
         <v>82</v>
       </c>
       <c r="AM86" t="s" s="2">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="AN86" t="s" s="2">
         <v>82</v>
@@ -12540,10 +12535,10 @@
     </row>
     <row r="87">
       <c r="A87" t="s" s="2">
-        <v>532</v>
+        <v>531</v>
       </c>
       <c r="B87" t="s" s="2">
-        <v>532</v>
+        <v>531</v>
       </c>
       <c r="C87" s="2"/>
       <c r="D87" t="s" s="2">
@@ -12569,16 +12564,16 @@
         <v>223</v>
       </c>
       <c r="L87" t="s" s="2">
+        <v>532</v>
+      </c>
+      <c r="M87" t="s" s="2">
         <v>533</v>
       </c>
-      <c r="M87" t="s" s="2">
+      <c r="N87" t="s" s="2">
         <v>534</v>
       </c>
-      <c r="N87" t="s" s="2">
+      <c r="O87" t="s" s="2">
         <v>535</v>
-      </c>
-      <c r="O87" t="s" s="2">
-        <v>536</v>
       </c>
       <c r="P87" t="s" s="2">
         <v>82</v>
@@ -12627,7 +12622,7 @@
         <v>82</v>
       </c>
       <c r="AF87" t="s" s="2">
-        <v>532</v>
+        <v>531</v>
       </c>
       <c r="AG87" t="s" s="2">
         <v>80</v>
@@ -12645,10 +12640,10 @@
         <v>82</v>
       </c>
       <c r="AL87" t="s" s="2">
+        <v>536</v>
+      </c>
+      <c r="AM87" t="s" s="2">
         <v>537</v>
-      </c>
-      <c r="AM87" t="s" s="2">
-        <v>538</v>
       </c>
       <c r="AN87" t="s" s="2">
         <v>82</v>
@@ -12659,10 +12654,10 @@
     </row>
     <row r="88">
       <c r="A88" t="s" s="2">
-        <v>539</v>
+        <v>538</v>
       </c>
       <c r="B88" t="s" s="2">
-        <v>539</v>
+        <v>538</v>
       </c>
       <c r="C88" s="2"/>
       <c r="D88" t="s" s="2">
@@ -12774,10 +12769,10 @@
     </row>
     <row r="89">
       <c r="A89" t="s" s="2">
-        <v>540</v>
+        <v>539</v>
       </c>
       <c r="B89" t="s" s="2">
-        <v>540</v>
+        <v>539</v>
       </c>
       <c r="C89" s="2"/>
       <c r="D89" t="s" s="2">
@@ -12891,10 +12886,10 @@
     </row>
     <row r="90">
       <c r="A90" t="s" s="2">
-        <v>541</v>
+        <v>540</v>
       </c>
       <c r="B90" t="s" s="2">
-        <v>541</v>
+        <v>540</v>
       </c>
       <c r="C90" s="2"/>
       <c r="D90" t="s" s="2">
@@ -12917,16 +12912,16 @@
         <v>92</v>
       </c>
       <c r="K90" t="s" s="2">
-        <v>380</v>
+        <v>379</v>
       </c>
       <c r="L90" t="s" s="2">
+        <v>541</v>
+      </c>
+      <c r="M90" t="s" s="2">
         <v>542</v>
       </c>
-      <c r="M90" t="s" s="2">
+      <c r="N90" t="s" s="2">
         <v>543</v>
-      </c>
-      <c r="N90" t="s" s="2">
-        <v>544</v>
       </c>
       <c r="O90" s="2"/>
       <c r="P90" t="s" s="2">
@@ -12976,16 +12971,16 @@
         <v>82</v>
       </c>
       <c r="AF90" t="s" s="2">
+        <v>544</v>
+      </c>
+      <c r="AG90" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH90" t="s" s="2">
+        <v>91</v>
+      </c>
+      <c r="AI90" t="s" s="2">
         <v>545</v>
-      </c>
-      <c r="AG90" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AH90" t="s" s="2">
-        <v>91</v>
-      </c>
-      <c r="AI90" t="s" s="2">
-        <v>546</v>
       </c>
       <c r="AJ90" t="s" s="2">
         <v>103</v>
@@ -12997,21 +12992,21 @@
         <v>82</v>
       </c>
       <c r="AM90" t="s" s="2">
+        <v>546</v>
+      </c>
+      <c r="AN90" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AO90" t="s" s="2">
         <v>547</v>
-      </c>
-      <c r="AN90" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AO90" t="s" s="2">
-        <v>548</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="s" s="2">
-        <v>549</v>
+        <v>548</v>
       </c>
       <c r="B91" t="s" s="2">
-        <v>549</v>
+        <v>548</v>
       </c>
       <c r="C91" s="2"/>
       <c r="D91" t="s" s="2">
@@ -13034,69 +13029,69 @@
         <v>92</v>
       </c>
       <c r="K91" t="s" s="2">
-        <v>380</v>
+        <v>379</v>
       </c>
       <c r="L91" t="s" s="2">
+        <v>549</v>
+      </c>
+      <c r="M91" t="s" s="2">
         <v>550</v>
       </c>
-      <c r="M91" t="s" s="2">
+      <c r="N91" t="s" s="2">
         <v>551</v>
-      </c>
-      <c r="N91" t="s" s="2">
-        <v>552</v>
       </c>
       <c r="O91" s="2"/>
       <c r="P91" t="s" s="2">
         <v>82</v>
       </c>
       <c r="Q91" t="s" s="2">
+        <v>552</v>
+      </c>
+      <c r="R91" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="S91" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="T91" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="U91" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="V91" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="W91" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="X91" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Y91" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Z91" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AA91" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AB91" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AC91" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AD91" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AE91" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AF91" t="s" s="2">
         <v>553</v>
       </c>
-      <c r="R91" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="S91" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="T91" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="U91" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="V91" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="W91" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="X91" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Y91" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Z91" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AA91" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AB91" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AC91" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AD91" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AE91" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AF91" t="s" s="2">
-        <v>554</v>
-      </c>
       <c r="AG91" t="s" s="2">
         <v>80</v>
       </c>
@@ -13104,7 +13099,7 @@
         <v>91</v>
       </c>
       <c r="AI91" t="s" s="2">
-        <v>546</v>
+        <v>545</v>
       </c>
       <c r="AJ91" t="s" s="2">
         <v>103</v>
@@ -13116,21 +13111,21 @@
         <v>82</v>
       </c>
       <c r="AM91" t="s" s="2">
+        <v>554</v>
+      </c>
+      <c r="AN91" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AO91" t="s" s="2">
         <v>555</v>
-      </c>
-      <c r="AN91" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AO91" t="s" s="2">
-        <v>556</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="s" s="2">
-        <v>557</v>
+        <v>556</v>
       </c>
       <c r="B92" t="s" s="2">
-        <v>557</v>
+        <v>556</v>
       </c>
       <c r="C92" s="2"/>
       <c r="D92" t="s" s="2">
@@ -13153,16 +13148,16 @@
         <v>82</v>
       </c>
       <c r="K92" t="s" s="2">
+        <v>557</v>
+      </c>
+      <c r="L92" t="s" s="2">
         <v>558</v>
       </c>
-      <c r="L92" t="s" s="2">
+      <c r="M92" t="s" s="2">
         <v>559</v>
       </c>
-      <c r="M92" t="s" s="2">
+      <c r="N92" t="s" s="2">
         <v>560</v>
-      </c>
-      <c r="N92" t="s" s="2">
-        <v>561</v>
       </c>
       <c r="O92" s="2"/>
       <c r="P92" t="s" s="2">
@@ -13212,7 +13207,7 @@
         <v>82</v>
       </c>
       <c r="AF92" t="s" s="2">
-        <v>557</v>
+        <v>556</v>
       </c>
       <c r="AG92" t="s" s="2">
         <v>80</v>
@@ -13230,24 +13225,24 @@
         <v>82</v>
       </c>
       <c r="AL92" t="s" s="2">
+        <v>561</v>
+      </c>
+      <c r="AM92" t="s" s="2">
         <v>562</v>
       </c>
-      <c r="AM92" t="s" s="2">
+      <c r="AN92" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AO92" t="s" s="2">
         <v>563</v>
-      </c>
-      <c r="AN92" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AO92" t="s" s="2">
-        <v>564</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="s" s="2">
-        <v>565</v>
+        <v>564</v>
       </c>
       <c r="B93" t="s" s="2">
-        <v>565</v>
+        <v>564</v>
       </c>
       <c r="C93" s="2"/>
       <c r="D93" t="s" s="2">
@@ -13270,16 +13265,16 @@
         <v>82</v>
       </c>
       <c r="K93" t="s" s="2">
-        <v>519</v>
+        <v>518</v>
       </c>
       <c r="L93" t="s" s="2">
+        <v>565</v>
+      </c>
+      <c r="M93" t="s" s="2">
         <v>566</v>
       </c>
-      <c r="M93" t="s" s="2">
+      <c r="N93" t="s" s="2">
         <v>567</v>
-      </c>
-      <c r="N93" t="s" s="2">
-        <v>568</v>
       </c>
       <c r="O93" s="2"/>
       <c r="P93" t="s" s="2">
@@ -13329,7 +13324,7 @@
         <v>82</v>
       </c>
       <c r="AF93" t="s" s="2">
-        <v>565</v>
+        <v>564</v>
       </c>
       <c r="AG93" t="s" s="2">
         <v>80</v>
@@ -13347,24 +13342,24 @@
         <v>82</v>
       </c>
       <c r="AL93" t="s" s="2">
+        <v>568</v>
+      </c>
+      <c r="AM93" t="s" s="2">
         <v>569</v>
       </c>
-      <c r="AM93" t="s" s="2">
+      <c r="AN93" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AO93" t="s" s="2">
         <v>570</v>
-      </c>
-      <c r="AN93" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AO93" t="s" s="2">
-        <v>571</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="s" s="2">
-        <v>572</v>
+        <v>571</v>
       </c>
       <c r="B94" t="s" s="2">
-        <v>572</v>
+        <v>571</v>
       </c>
       <c r="C94" s="2"/>
       <c r="D94" t="s" s="2">
@@ -13387,16 +13382,16 @@
         <v>82</v>
       </c>
       <c r="K94" t="s" s="2">
-        <v>525</v>
+        <v>524</v>
       </c>
       <c r="L94" t="s" s="2">
+        <v>572</v>
+      </c>
+      <c r="M94" t="s" s="2">
         <v>573</v>
       </c>
-      <c r="M94" t="s" s="2">
+      <c r="N94" t="s" s="2">
         <v>574</v>
-      </c>
-      <c r="N94" t="s" s="2">
-        <v>575</v>
       </c>
       <c r="O94" s="2"/>
       <c r="P94" t="s" s="2">
@@ -13446,7 +13441,7 @@
         <v>82</v>
       </c>
       <c r="AF94" t="s" s="2">
-        <v>572</v>
+        <v>571</v>
       </c>
       <c r="AG94" t="s" s="2">
         <v>80</v>
@@ -13464,10 +13459,10 @@
         <v>82</v>
       </c>
       <c r="AL94" t="s" s="2">
+        <v>575</v>
+      </c>
+      <c r="AM94" t="s" s="2">
         <v>576</v>
-      </c>
-      <c r="AM94" t="s" s="2">
-        <v>577</v>
       </c>
       <c r="AN94" t="s" s="2">
         <v>82</v>
@@ -13478,10 +13473,10 @@
     </row>
     <row r="95">
       <c r="A95" t="s" s="2">
-        <v>578</v>
+        <v>577</v>
       </c>
       <c r="B95" t="s" s="2">
-        <v>578</v>
+        <v>577</v>
       </c>
       <c r="C95" s="2"/>
       <c r="D95" t="s" s="2">
@@ -13593,10 +13588,10 @@
     </row>
     <row r="96">
       <c r="A96" t="s" s="2">
-        <v>579</v>
+        <v>578</v>
       </c>
       <c r="B96" t="s" s="2">
-        <v>579</v>
+        <v>578</v>
       </c>
       <c r="C96" s="2"/>
       <c r="D96" t="s" s="2">
@@ -13710,10 +13705,10 @@
     </row>
     <row r="97">
       <c r="A97" t="s" s="2">
-        <v>580</v>
+        <v>579</v>
       </c>
       <c r="B97" t="s" s="2">
-        <v>580</v>
+        <v>579</v>
       </c>
       <c r="C97" s="2"/>
       <c r="D97" t="s" s="2">
@@ -13736,19 +13731,19 @@
         <v>92</v>
       </c>
       <c r="K97" t="s" s="2">
+        <v>580</v>
+      </c>
+      <c r="L97" t="s" s="2">
         <v>581</v>
       </c>
-      <c r="L97" t="s" s="2">
+      <c r="M97" t="s" s="2">
         <v>582</v>
       </c>
-      <c r="M97" t="s" s="2">
+      <c r="N97" t="s" s="2">
         <v>583</v>
       </c>
-      <c r="N97" t="s" s="2">
+      <c r="O97" t="s" s="2">
         <v>584</v>
-      </c>
-      <c r="O97" t="s" s="2">
-        <v>585</v>
       </c>
       <c r="P97" t="s" s="2">
         <v>82</v>
@@ -13797,7 +13792,7 @@
         <v>82</v>
       </c>
       <c r="AF97" t="s" s="2">
-        <v>586</v>
+        <v>585</v>
       </c>
       <c r="AG97" t="s" s="2">
         <v>80</v>
@@ -13818,21 +13813,21 @@
         <v>82</v>
       </c>
       <c r="AM97" t="s" s="2">
+        <v>586</v>
+      </c>
+      <c r="AN97" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AO97" t="s" s="2">
         <v>587</v>
-      </c>
-      <c r="AN97" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AO97" t="s" s="2">
-        <v>588</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="s" s="2">
-        <v>589</v>
+        <v>588</v>
       </c>
       <c r="B98" t="s" s="2">
-        <v>589</v>
+        <v>588</v>
       </c>
       <c r="C98" s="2"/>
       <c r="D98" t="s" s="2">
@@ -13858,20 +13853,20 @@
         <v>111</v>
       </c>
       <c r="L98" t="s" s="2">
+        <v>589</v>
+      </c>
+      <c r="M98" t="s" s="2">
         <v>590</v>
-      </c>
-      <c r="M98" t="s" s="2">
-        <v>591</v>
       </c>
       <c r="N98" s="2"/>
       <c r="O98" t="s" s="2">
+        <v>591</v>
+      </c>
+      <c r="P98" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Q98" t="s" s="2">
         <v>592</v>
-      </c>
-      <c r="P98" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Q98" t="s" s="2">
-        <v>593</v>
       </c>
       <c r="R98" t="s" s="2">
         <v>82</v>
@@ -13895,28 +13890,28 @@
         <v>186</v>
       </c>
       <c r="Y98" t="s" s="2">
+        <v>593</v>
+      </c>
+      <c r="Z98" t="s" s="2">
         <v>594</v>
       </c>
-      <c r="Z98" t="s" s="2">
+      <c r="AA98" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AB98" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AC98" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AD98" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AE98" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AF98" t="s" s="2">
         <v>595</v>
-      </c>
-      <c r="AA98" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AB98" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AC98" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AD98" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AE98" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AF98" t="s" s="2">
-        <v>596</v>
       </c>
       <c r="AG98" t="s" s="2">
         <v>80</v>
@@ -13937,21 +13932,21 @@
         <v>82</v>
       </c>
       <c r="AM98" t="s" s="2">
+        <v>596</v>
+      </c>
+      <c r="AN98" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AO98" t="s" s="2">
         <v>597</v>
-      </c>
-      <c r="AN98" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AO98" t="s" s="2">
-        <v>598</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="s" s="2">
-        <v>599</v>
+        <v>598</v>
       </c>
       <c r="B99" t="s" s="2">
-        <v>599</v>
+        <v>598</v>
       </c>
       <c r="C99" s="2"/>
       <c r="D99" t="s" s="2">
@@ -13977,63 +13972,63 @@
         <v>169</v>
       </c>
       <c r="L99" t="s" s="2">
+        <v>599</v>
+      </c>
+      <c r="M99" t="s" s="2">
         <v>600</v>
-      </c>
-      <c r="M99" t="s" s="2">
-        <v>601</v>
       </c>
       <c r="N99" s="2"/>
       <c r="O99" t="s" s="2">
-        <v>602</v>
+        <v>601</v>
       </c>
       <c r="P99" t="s" s="2">
         <v>82</v>
       </c>
       <c r="Q99" s="2"/>
       <c r="R99" t="s" s="2">
+        <v>602</v>
+      </c>
+      <c r="S99" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="T99" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="U99" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="V99" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="W99" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="X99" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Y99" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Z99" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AA99" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AB99" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AC99" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AD99" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AE99" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AF99" t="s" s="2">
         <v>603</v>
-      </c>
-      <c r="S99" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="T99" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="U99" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="V99" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="W99" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="X99" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Y99" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Z99" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AA99" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AB99" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AC99" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AD99" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AE99" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AF99" t="s" s="2">
-        <v>604</v>
       </c>
       <c r="AG99" t="s" s="2">
         <v>80</v>
@@ -14054,21 +14049,21 @@
         <v>82</v>
       </c>
       <c r="AM99" t="s" s="2">
+        <v>604</v>
+      </c>
+      <c r="AN99" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AO99" t="s" s="2">
         <v>605</v>
-      </c>
-      <c r="AN99" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AO99" t="s" s="2">
-        <v>606</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="s" s="2">
-        <v>607</v>
+        <v>606</v>
       </c>
       <c r="B100" t="s" s="2">
-        <v>607</v>
+        <v>606</v>
       </c>
       <c r="C100" s="2"/>
       <c r="D100" t="s" s="2">
@@ -14094,72 +14089,72 @@
         <v>105</v>
       </c>
       <c r="L100" t="s" s="2">
+        <v>607</v>
+      </c>
+      <c r="M100" t="s" s="2">
         <v>608</v>
-      </c>
-      <c r="M100" t="s" s="2">
-        <v>609</v>
       </c>
       <c r="N100" s="2"/>
       <c r="O100" t="s" s="2">
-        <v>610</v>
+        <v>609</v>
       </c>
       <c r="P100" t="s" s="2">
         <v>82</v>
       </c>
       <c r="Q100" s="2"/>
       <c r="R100" t="s" s="2">
+        <v>610</v>
+      </c>
+      <c r="S100" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="T100" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="U100" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="V100" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="W100" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="X100" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Y100" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Z100" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AA100" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AB100" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AC100" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AD100" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AE100" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AF100" t="s" s="2">
         <v>611</v>
       </c>
-      <c r="S100" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="T100" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="U100" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="V100" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="W100" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="X100" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Y100" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Z100" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AA100" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AB100" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AC100" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AD100" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AE100" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AF100" t="s" s="2">
+      <c r="AG100" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH100" t="s" s="2">
+        <v>91</v>
+      </c>
+      <c r="AI100" t="s" s="2">
         <v>612</v>
-      </c>
-      <c r="AG100" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AH100" t="s" s="2">
-        <v>91</v>
-      </c>
-      <c r="AI100" t="s" s="2">
-        <v>613</v>
       </c>
       <c r="AJ100" t="s" s="2">
         <v>103</v>
@@ -14171,21 +14166,21 @@
         <v>82</v>
       </c>
       <c r="AM100" t="s" s="2">
-        <v>614</v>
+        <v>613</v>
       </c>
       <c r="AN100" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AO100" t="s" s="2">
-        <v>606</v>
+        <v>605</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="s" s="2">
-        <v>615</v>
+        <v>614</v>
       </c>
       <c r="B101" t="s" s="2">
-        <v>615</v>
+        <v>614</v>
       </c>
       <c r="C101" s="2"/>
       <c r="D101" t="s" s="2">
@@ -14211,65 +14206,65 @@
         <v>111</v>
       </c>
       <c r="L101" t="s" s="2">
+        <v>615</v>
+      </c>
+      <c r="M101" t="s" s="2">
         <v>616</v>
       </c>
-      <c r="M101" t="s" s="2">
+      <c r="N101" t="s" s="2">
         <v>617</v>
       </c>
-      <c r="N101" t="s" s="2">
+      <c r="O101" t="s" s="2">
         <v>618</v>
-      </c>
-      <c r="O101" t="s" s="2">
-        <v>619</v>
       </c>
       <c r="P101" t="s" s="2">
         <v>82</v>
       </c>
       <c r="Q101" s="2"/>
       <c r="R101" t="s" s="2">
+        <v>619</v>
+      </c>
+      <c r="S101" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="T101" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="U101" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="V101" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="W101" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="X101" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Y101" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Z101" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AA101" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AB101" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AC101" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AD101" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AE101" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AF101" t="s" s="2">
         <v>620</v>
-      </c>
-      <c r="S101" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="T101" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="U101" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="V101" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="W101" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="X101" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Y101" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Z101" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AA101" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AB101" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AC101" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AD101" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AE101" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AF101" t="s" s="2">
-        <v>621</v>
       </c>
       <c r="AG101" t="s" s="2">
         <v>80</v>
@@ -14290,21 +14285,21 @@
         <v>82</v>
       </c>
       <c r="AM101" t="s" s="2">
-        <v>622</v>
+        <v>621</v>
       </c>
       <c r="AN101" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AO101" t="s" s="2">
-        <v>606</v>
+        <v>605</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="s" s="2">
-        <v>623</v>
+        <v>622</v>
       </c>
       <c r="B102" t="s" s="2">
-        <v>623</v>
+        <v>622</v>
       </c>
       <c r="C102" s="2"/>
       <c r="D102" t="s" s="2">
@@ -14327,16 +14322,16 @@
         <v>82</v>
       </c>
       <c r="K102" t="s" s="2">
+        <v>623</v>
+      </c>
+      <c r="L102" t="s" s="2">
         <v>624</v>
       </c>
-      <c r="L102" t="s" s="2">
+      <c r="M102" t="s" s="2">
         <v>625</v>
       </c>
-      <c r="M102" t="s" s="2">
-        <v>626</v>
-      </c>
       <c r="N102" t="s" s="2">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="O102" s="2"/>
       <c r="P102" t="s" s="2">
@@ -14386,7 +14381,7 @@
         <v>82</v>
       </c>
       <c r="AF102" t="s" s="2">
-        <v>623</v>
+        <v>622</v>
       </c>
       <c r="AG102" t="s" s="2">
         <v>80</v>
@@ -14407,10 +14402,10 @@
         <v>82</v>
       </c>
       <c r="AM102" t="s" s="2">
-        <v>627</v>
+        <v>626</v>
       </c>
       <c r="AN102" t="s" s="2">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="AO102" t="s" s="2">
         <v>82</v>
@@ -14418,10 +14413,10 @@
     </row>
     <row r="103">
       <c r="A103" t="s" s="2">
-        <v>628</v>
+        <v>627</v>
       </c>
       <c r="B103" t="s" s="2">
-        <v>628</v>
+        <v>627</v>
       </c>
       <c r="C103" s="2"/>
       <c r="D103" t="s" s="2">
@@ -14444,13 +14439,13 @@
         <v>82</v>
       </c>
       <c r="K103" t="s" s="2">
-        <v>483</v>
+        <v>482</v>
       </c>
       <c r="L103" t="s" s="2">
+        <v>628</v>
+      </c>
+      <c r="M103" t="s" s="2">
         <v>629</v>
-      </c>
-      <c r="M103" t="s" s="2">
-        <v>630</v>
       </c>
       <c r="N103" s="2"/>
       <c r="O103" s="2"/>
@@ -14501,7 +14496,7 @@
         <v>82</v>
       </c>
       <c r="AF103" t="s" s="2">
-        <v>628</v>
+        <v>627</v>
       </c>
       <c r="AG103" t="s" s="2">
         <v>80</v>
@@ -14519,10 +14514,10 @@
         <v>82</v>
       </c>
       <c r="AL103" t="s" s="2">
+        <v>630</v>
+      </c>
+      <c r="AM103" t="s" s="2">
         <v>631</v>
-      </c>
-      <c r="AM103" t="s" s="2">
-        <v>632</v>
       </c>
       <c r="AN103" t="s" s="2">
         <v>82</v>
@@ -14533,10 +14528,10 @@
     </row>
     <row r="104">
       <c r="A104" t="s" s="2">
-        <v>633</v>
+        <v>632</v>
       </c>
       <c r="B104" t="s" s="2">
-        <v>633</v>
+        <v>632</v>
       </c>
       <c r="C104" s="2"/>
       <c r="D104" t="s" s="2">
@@ -14648,10 +14643,10 @@
     </row>
     <row r="105">
       <c r="A105" t="s" s="2">
-        <v>634</v>
+        <v>633</v>
       </c>
       <c r="B105" t="s" s="2">
-        <v>634</v>
+        <v>633</v>
       </c>
       <c r="C105" s="2"/>
       <c r="D105" t="s" s="2">
@@ -14765,14 +14760,14 @@
     </row>
     <row r="106">
       <c r="A106" t="s" s="2">
-        <v>635</v>
+        <v>634</v>
       </c>
       <c r="B106" t="s" s="2">
-        <v>635</v>
+        <v>634</v>
       </c>
       <c r="C106" s="2"/>
       <c r="D106" t="s" s="2">
-        <v>506</v>
+        <v>505</v>
       </c>
       <c r="E106" s="2"/>
       <c r="F106" t="s" s="2">
@@ -14794,10 +14789,10 @@
         <v>137</v>
       </c>
       <c r="L106" t="s" s="2">
+        <v>506</v>
+      </c>
+      <c r="M106" t="s" s="2">
         <v>507</v>
-      </c>
-      <c r="M106" t="s" s="2">
-        <v>508</v>
       </c>
       <c r="N106" t="s" s="2">
         <v>140</v>
@@ -14852,7 +14847,7 @@
         <v>82</v>
       </c>
       <c r="AF106" t="s" s="2">
-        <v>509</v>
+        <v>508</v>
       </c>
       <c r="AG106" t="s" s="2">
         <v>80</v>
@@ -14884,10 +14879,10 @@
     </row>
     <row r="107">
       <c r="A107" t="s" s="2">
-        <v>636</v>
+        <v>635</v>
       </c>
       <c r="B107" t="s" s="2">
-        <v>636</v>
+        <v>635</v>
       </c>
       <c r="C107" s="2"/>
       <c r="D107" t="s" s="2">
@@ -14913,13 +14908,13 @@
         <v>193</v>
       </c>
       <c r="L107" t="s" s="2">
-        <v>629</v>
+        <v>628</v>
       </c>
       <c r="M107" t="s" s="2">
+        <v>636</v>
+      </c>
+      <c r="N107" t="s" s="2">
         <v>637</v>
-      </c>
-      <c r="N107" t="s" s="2">
-        <v>638</v>
       </c>
       <c r="O107" s="2"/>
       <c r="P107" t="s" s="2">
@@ -14949,7 +14944,7 @@
       </c>
       <c r="Y107" s="2"/>
       <c r="Z107" t="s" s="2">
-        <v>639</v>
+        <v>638</v>
       </c>
       <c r="AA107" t="s" s="2">
         <v>82</v>
@@ -14967,7 +14962,7 @@
         <v>82</v>
       </c>
       <c r="AF107" t="s" s="2">
-        <v>636</v>
+        <v>635</v>
       </c>
       <c r="AG107" t="s" s="2">
         <v>91</v>
@@ -14985,24 +14980,24 @@
         <v>82</v>
       </c>
       <c r="AL107" t="s" s="2">
-        <v>631</v>
+        <v>630</v>
       </c>
       <c r="AM107" t="s" s="2">
+        <v>639</v>
+      </c>
+      <c r="AN107" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AO107" t="s" s="2">
         <v>640</v>
-      </c>
-      <c r="AN107" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AO107" t="s" s="2">
-        <v>641</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="s" s="2">
-        <v>642</v>
+        <v>641</v>
       </c>
       <c r="B108" t="s" s="2">
-        <v>642</v>
+        <v>641</v>
       </c>
       <c r="C108" s="2"/>
       <c r="D108" t="s" s="2">
@@ -15028,13 +15023,13 @@
         <v>193</v>
       </c>
       <c r="L108" t="s" s="2">
+        <v>642</v>
+      </c>
+      <c r="M108" t="s" s="2">
         <v>643</v>
       </c>
-      <c r="M108" t="s" s="2">
+      <c r="N108" t="s" s="2">
         <v>644</v>
-      </c>
-      <c r="N108" t="s" s="2">
-        <v>645</v>
       </c>
       <c r="O108" s="2"/>
       <c r="P108" t="s" s="2">
@@ -15064,7 +15059,7 @@
       </c>
       <c r="Y108" s="2"/>
       <c r="Z108" t="s" s="2">
-        <v>646</v>
+        <v>645</v>
       </c>
       <c r="AA108" t="s" s="2">
         <v>82</v>
@@ -15082,7 +15077,7 @@
         <v>82</v>
       </c>
       <c r="AF108" t="s" s="2">
-        <v>642</v>
+        <v>641</v>
       </c>
       <c r="AG108" t="s" s="2">
         <v>80</v>
@@ -15100,24 +15095,24 @@
         <v>82</v>
       </c>
       <c r="AL108" t="s" s="2">
+        <v>646</v>
+      </c>
+      <c r="AM108" t="s" s="2">
         <v>647</v>
       </c>
-      <c r="AM108" t="s" s="2">
+      <c r="AN108" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AO108" t="s" s="2">
         <v>648</v>
-      </c>
-      <c r="AN108" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AO108" t="s" s="2">
-        <v>649</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="s" s="2">
-        <v>650</v>
+        <v>649</v>
       </c>
       <c r="B109" t="s" s="2">
-        <v>650</v>
+        <v>649</v>
       </c>
       <c r="C109" s="2"/>
       <c r="D109" t="s" s="2">
@@ -15140,16 +15135,16 @@
         <v>82</v>
       </c>
       <c r="K109" t="s" s="2">
+        <v>650</v>
+      </c>
+      <c r="L109" t="s" s="2">
         <v>651</v>
       </c>
-      <c r="L109" t="s" s="2">
+      <c r="M109" t="s" s="2">
         <v>652</v>
       </c>
-      <c r="M109" t="s" s="2">
-        <v>653</v>
-      </c>
       <c r="N109" t="s" s="2">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="O109" s="2"/>
       <c r="P109" t="s" s="2">
@@ -15199,7 +15194,7 @@
         <v>82</v>
       </c>
       <c r="AF109" t="s" s="2">
-        <v>650</v>
+        <v>649</v>
       </c>
       <c r="AG109" t="s" s="2">
         <v>80</v>
@@ -15214,13 +15209,13 @@
         <v>103</v>
       </c>
       <c r="AK109" t="s" s="2">
+        <v>653</v>
+      </c>
+      <c r="AL109" t="s" s="2">
+        <v>646</v>
+      </c>
+      <c r="AM109" t="s" s="2">
         <v>654</v>
-      </c>
-      <c r="AL109" t="s" s="2">
-        <v>647</v>
-      </c>
-      <c r="AM109" t="s" s="2">
-        <v>655</v>
       </c>
       <c r="AN109" t="s" s="2">
         <v>82</v>
@@ -15231,14 +15226,14 @@
     </row>
     <row r="110">
       <c r="A110" t="s" s="2">
-        <v>656</v>
+        <v>655</v>
       </c>
       <c r="B110" t="s" s="2">
-        <v>656</v>
+        <v>655</v>
       </c>
       <c r="C110" s="2"/>
       <c r="D110" t="s" s="2">
-        <v>657</v>
+        <v>656</v>
       </c>
       <c r="E110" s="2"/>
       <c r="F110" t="s" s="2">
@@ -15257,16 +15252,16 @@
         <v>82</v>
       </c>
       <c r="K110" t="s" s="2">
+        <v>657</v>
+      </c>
+      <c r="L110" t="s" s="2">
         <v>658</v>
       </c>
-      <c r="L110" t="s" s="2">
+      <c r="M110" t="s" s="2">
         <v>659</v>
       </c>
-      <c r="M110" t="s" s="2">
+      <c r="N110" t="s" s="2">
         <v>660</v>
-      </c>
-      <c r="N110" t="s" s="2">
-        <v>661</v>
       </c>
       <c r="O110" s="2"/>
       <c r="P110" t="s" s="2">
@@ -15316,7 +15311,7 @@
         <v>82</v>
       </c>
       <c r="AF110" t="s" s="2">
-        <v>656</v>
+        <v>655</v>
       </c>
       <c r="AG110" t="s" s="2">
         <v>80</v>
@@ -15337,7 +15332,7 @@
         <v>82</v>
       </c>
       <c r="AM110" t="s" s="2">
-        <v>662</v>
+        <v>661</v>
       </c>
       <c r="AN110" t="s" s="2">
         <v>82</v>
@@ -15348,10 +15343,10 @@
     </row>
     <row r="111">
       <c r="A111" t="s" s="2">
-        <v>663</v>
+        <v>662</v>
       </c>
       <c r="B111" t="s" s="2">
-        <v>663</v>
+        <v>662</v>
       </c>
       <c r="C111" s="2"/>
       <c r="D111" t="s" s="2">
@@ -15374,16 +15369,16 @@
         <v>82</v>
       </c>
       <c r="K111" t="s" s="2">
+        <v>663</v>
+      </c>
+      <c r="L111" t="s" s="2">
         <v>664</v>
       </c>
-      <c r="L111" t="s" s="2">
+      <c r="M111" t="s" s="2">
         <v>665</v>
       </c>
-      <c r="M111" t="s" s="2">
+      <c r="N111" t="s" s="2">
         <v>666</v>
-      </c>
-      <c r="N111" t="s" s="2">
-        <v>667</v>
       </c>
       <c r="O111" s="2"/>
       <c r="P111" t="s" s="2">
@@ -15433,7 +15428,7 @@
         <v>82</v>
       </c>
       <c r="AF111" t="s" s="2">
-        <v>663</v>
+        <v>662</v>
       </c>
       <c r="AG111" t="s" s="2">
         <v>80</v>
@@ -15448,13 +15443,13 @@
         <v>103</v>
       </c>
       <c r="AK111" t="s" s="2">
+        <v>667</v>
+      </c>
+      <c r="AL111" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM111" t="s" s="2">
         <v>668</v>
-      </c>
-      <c r="AL111" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AM111" t="s" s="2">
-        <v>669</v>
       </c>
       <c r="AN111" t="s" s="2">
         <v>82</v>
